--- a/AAII_Financials/Quarterly/GWLL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GWLL_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>GWLL</t>
   </si>
@@ -656,80 +656,87 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -772,8 +779,14 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -786,14 +799,14 @@
       <c r="F9" s="3">
         <v>0</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>4</v>
+      <c r="G9" s="3">
+        <v>0</v>
       </c>
       <c r="H9" s="3">
         <v>0</v>
       </c>
-      <c r="I9" s="3">
-        <v>0</v>
+      <c r="I9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
@@ -807,17 +820,23 @@
       <c r="M9" s="3">
         <v>0</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>4</v>
+      <c r="N9" s="3">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -830,14 +849,14 @@
       <c r="F10" s="3">
         <v>0</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
+      <c r="G10" s="3">
+        <v>0</v>
       </c>
       <c r="H10" s="3">
         <v>0</v>
       </c>
-      <c r="I10" s="3">
-        <v>0</v>
+      <c r="I10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J10" s="3">
         <v>0</v>
@@ -851,17 +870,23 @@
       <c r="M10" s="3">
         <v>0</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>4</v>
+      <c r="N10" s="3">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,8 +903,10 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -922,8 +949,14 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,8 +999,14 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1010,8 +1049,14 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1054,8 +1099,14 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,13 +1120,15 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>4</v>
+      <c r="D17" s="3">
+        <v>0</v>
       </c>
       <c r="E17" s="3">
         <v>0</v>
@@ -1084,14 +1137,14 @@
         <v>0</v>
       </c>
       <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3">
         <v>900</v>
       </c>
-      <c r="H17" s="3">
-        <v>0</v>
-      </c>
-      <c r="I17" s="3">
-        <v>0</v>
-      </c>
       <c r="J17" s="3">
         <v>0</v>
       </c>
@@ -1113,8 +1166,14 @@
       <c r="P17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3">
+        <v>0</v>
+      </c>
+      <c r="R17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1128,14 +1187,14 @@
         <v>0</v>
       </c>
       <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
         <v>-900</v>
       </c>
-      <c r="H18" s="3">
-        <v>0</v>
-      </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
       <c r="J18" s="3">
         <v>0</v>
       </c>
@@ -1157,8 +1216,14 @@
       <c r="P18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3">
+        <v>0</v>
+      </c>
+      <c r="R18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,8 +1240,10 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1219,8 +1286,14 @@
       <c r="P20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1233,11 +1306,11 @@
       <c r="F21" s="3">
         <v>0</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>4</v>
@@ -1245,11 +1318,11 @@
       <c r="J21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3">
-        <v>0</v>
+      <c r="K21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M21" s="3">
         <v>0</v>
@@ -1257,14 +1330,20 @@
       <c r="N21" s="3">
         <v>0</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O21" s="3">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1307,13 +1386,19 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>4</v>
+      <c r="D23" s="3">
+        <v>0</v>
       </c>
       <c r="E23" s="3">
         <v>0</v>
@@ -1322,14 +1407,14 @@
         <v>0</v>
       </c>
       <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
         <v>-900</v>
       </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
       <c r="J23" s="3">
         <v>0</v>
       </c>
@@ -1351,8 +1436,14 @@
       <c r="P23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3">
+        <v>0</v>
+      </c>
+      <c r="R23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1395,8 +1486,14 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,13 +1536,19 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>4</v>
+      <c r="D26" s="3">
+        <v>0</v>
       </c>
       <c r="E26" s="3">
         <v>0</v>
@@ -1454,14 +1557,14 @@
         <v>0</v>
       </c>
       <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
         <v>-900</v>
       </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
       <c r="J26" s="3">
         <v>0</v>
       </c>
@@ -1483,13 +1586,19 @@
       <c r="P26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>4</v>
+      <c r="D27" s="3">
+        <v>0</v>
       </c>
       <c r="E27" s="3">
         <v>0</v>
@@ -1498,14 +1607,14 @@
         <v>0</v>
       </c>
       <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
         <v>-900</v>
       </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
       <c r="J27" s="3">
         <v>0</v>
       </c>
@@ -1527,8 +1636,14 @@
       <c r="P27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1686,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1736,14 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1786,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,8 +1836,14 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1747,13 +1886,19 @@
       <c r="P32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>4</v>
+      <c r="D33" s="3">
+        <v>0</v>
       </c>
       <c r="E33" s="3">
         <v>0</v>
@@ -1762,14 +1907,14 @@
         <v>0</v>
       </c>
       <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
         <v>-900</v>
       </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
-      <c r="I33" s="3">
-        <v>0</v>
-      </c>
       <c r="J33" s="3">
         <v>0</v>
       </c>
@@ -1791,8 +1936,14 @@
       <c r="P33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,13 +1986,19 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>4</v>
+      <c r="D35" s="3">
+        <v>0</v>
       </c>
       <c r="E35" s="3">
         <v>0</v>
@@ -1850,14 +2007,14 @@
         <v>0</v>
       </c>
       <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
         <v>-900</v>
       </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
-      <c r="I35" s="3">
-        <v>0</v>
-      </c>
       <c r="J35" s="3">
         <v>0</v>
       </c>
@@ -1879,57 +2036,69 @@
       <c r="P35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2115,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,8 +2135,10 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -1973,7 +2146,7 @@
         <v>0</v>
       </c>
       <c r="E41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F41" s="3">
         <v>0</v>
@@ -1982,7 +2155,7 @@
         <v>0</v>
       </c>
       <c r="H41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I41" s="3">
         <v>0</v>
@@ -1991,16 +2164,16 @@
         <v>100</v>
       </c>
       <c r="K41" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L41" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M41" s="3">
         <v>200</v>
       </c>
       <c r="N41" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O41" s="3">
         <v>200</v>
@@ -2008,8 +2181,14 @@
       <c r="P41" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3">
+        <v>200</v>
+      </c>
+      <c r="R41" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2052,19 +2231,25 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G43" s="3">
         <v>0</v>
@@ -2072,11 +2257,11 @@
       <c r="H43" s="3">
         <v>0</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
+      <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3">
+        <v>0</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
@@ -2090,14 +2275,20 @@
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2132,16 +2323,22 @@
         <v>200</v>
       </c>
       <c r="N44" s="3">
+        <v>200</v>
+      </c>
+      <c r="O44" s="3">
+        <v>200</v>
+      </c>
+      <c r="P44" s="3">
         <v>100</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2184,13 +2381,19 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>4</v>
+      <c r="D46" s="3">
+        <v>200</v>
       </c>
       <c r="E46" s="3">
         <v>200</v>
@@ -2208,28 +2411,34 @@
         <v>200</v>
       </c>
       <c r="J46" s="3">
+        <v>200</v>
+      </c>
+      <c r="K46" s="3">
+        <v>200</v>
+      </c>
+      <c r="L46" s="3">
         <v>300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>400</v>
-      </c>
-      <c r="L46" s="3">
-        <v>400</v>
-      </c>
-      <c r="M46" s="3">
-        <v>500</v>
       </c>
       <c r="N46" s="3">
         <v>400</v>
       </c>
       <c r="O46" s="3">
+        <v>500</v>
+      </c>
+      <c r="P46" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q46" s="3">
         <v>200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2272,8 +2481,14 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2302,22 +2517,28 @@
         <v>0</v>
       </c>
       <c r="L48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3">
         <v>100</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O48" s="3">
+        <v>100</v>
+      </c>
+      <c r="P48" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2360,8 +2581,14 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2631,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,16 +2681,22 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>4</v>
+      <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>4</v>
@@ -2465,8 +2704,8 @@
       <c r="G52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>4</v>
@@ -2477,8 +2716,8 @@
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
+      <c r="L52" s="3">
+        <v>0</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>4</v>
@@ -2492,8 +2731,14 @@
       <c r="P52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,8 +2781,14 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -2554,34 +2805,40 @@
         <v>200</v>
       </c>
       <c r="H54" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I54" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J54" s="3">
         <v>300</v>
       </c>
       <c r="K54" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="L54" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="M54" s="3">
         <v>500</v>
       </c>
       <c r="N54" s="3">
+        <v>500</v>
+      </c>
+      <c r="O54" s="3">
+        <v>500</v>
+      </c>
+      <c r="P54" s="3">
         <v>400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2855,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,13 +2875,15 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>4</v>
+      <c r="D57" s="3">
+        <v>0</v>
       </c>
       <c r="E57" s="3">
         <v>0</v>
@@ -2643,25 +2904,31 @@
         <v>0</v>
       </c>
       <c r="K57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M57" s="3">
         <v>100</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>4</v>
+      <c r="N57" s="3">
+        <v>100</v>
+      </c>
+      <c r="O57" s="3">
+        <v>100</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2704,8 +2971,14 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2748,13 +3021,19 @@
       <c r="P59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+      <c r="R59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>4</v>
+      <c r="D60" s="3">
+        <v>0</v>
       </c>
       <c r="E60" s="3">
         <v>0</v>
@@ -2775,25 +3054,31 @@
         <v>0</v>
       </c>
       <c r="K60" s="3">
+        <v>0</v>
+      </c>
+      <c r="L60" s="3">
+        <v>0</v>
+      </c>
+      <c r="M60" s="3">
         <v>200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>100</v>
       </c>
-      <c r="N60" s="3">
-        <v>0</v>
-      </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2836,8 +3121,14 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2856,14 +3147,14 @@
       <c r="H62" s="3">
         <v>0</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
+      <c r="I62" s="3">
+        <v>0</v>
       </c>
       <c r="J62" s="3">
         <v>0</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -2874,14 +3165,20 @@
       <c r="N62" s="3">
         <v>0</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3221,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3271,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,8 +3321,14 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -3027,10 +3342,10 @@
         <v>100</v>
       </c>
       <c r="G66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I66" s="3">
         <v>0</v>
@@ -3039,25 +3354,31 @@
         <v>0</v>
       </c>
       <c r="K66" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L66" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M66" s="3">
         <v>200</v>
       </c>
       <c r="N66" s="3">
+        <v>200</v>
+      </c>
+      <c r="O66" s="3">
+        <v>200</v>
+      </c>
+      <c r="P66" s="3">
         <v>100</v>
       </c>
-      <c r="O66" s="3">
-        <v>0</v>
-      </c>
-      <c r="P66" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3">
+        <v>0</v>
+      </c>
+      <c r="R66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3395,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3441,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3491,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3541,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,37 +3591,43 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="E72" s="3">
         <v>-1200</v>
       </c>
       <c r="F72" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H72" s="3">
         <v>-1100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-1100</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-200</v>
       </c>
       <c r="J72" s="3">
         <v>-200</v>
       </c>
       <c r="K72" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="L72" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="M72" s="3">
         <v>-100</v>
@@ -3289,13 +3636,19 @@
         <v>-100</v>
       </c>
       <c r="O72" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="Q72" s="3">
+        <v>0</v>
+      </c>
+      <c r="R72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3691,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3741,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,8 +3791,14 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -3438,10 +3809,10 @@
         <v>100</v>
       </c>
       <c r="F76" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G76" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H76" s="3">
         <v>200</v>
@@ -3450,10 +3821,10 @@
         <v>200</v>
       </c>
       <c r="J76" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K76" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L76" s="3">
         <v>300</v>
@@ -3462,16 +3833,22 @@
         <v>300</v>
       </c>
       <c r="N76" s="3">
+        <v>300</v>
+      </c>
+      <c r="O76" s="3">
+        <v>300</v>
+      </c>
+      <c r="P76" s="3">
         <v>400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,62 +3891,74 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>4</v>
+      <c r="D81" s="3">
+        <v>0</v>
       </c>
       <c r="E81" s="3">
         <v>0</v>
@@ -3578,14 +3967,14 @@
         <v>0</v>
       </c>
       <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
         <v>-900</v>
       </c>
-      <c r="H81" s="3">
-        <v>0</v>
-      </c>
-      <c r="I81" s="3">
-        <v>0</v>
-      </c>
       <c r="J81" s="3">
         <v>0</v>
       </c>
@@ -3607,8 +3996,14 @@
       <c r="P81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,8 +4020,10 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3669,8 +4066,14 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +4116,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +4166,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4216,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4266,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,8 +4316,14 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3904,37 +4337,43 @@
         <v>0</v>
       </c>
       <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
         <v>-900</v>
       </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
       <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3">
         <v>-100</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
       <c r="M89" s="3">
         <v>0</v>
       </c>
       <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
         <v>-200</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,8 +4390,10 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3995,8 +4436,14 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4486,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,8 +4536,14 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4127,8 +4586,14 @@
       <c r="P94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4610,10 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4189,8 +4656,14 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4706,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4756,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,8 +4806,14 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4330,16 +4821,16 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>4</v>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>4</v>
@@ -4347,26 +4838,32 @@
       <c r="J100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4409,8 +4906,14 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4433,14 +4936,14 @@
         <v>0</v>
       </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
         <v>0</v>
       </c>
@@ -4451,6 +4954,12 @@
         <v>0</v>
       </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GWLL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GWLL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
   <si>
     <t>GWLL</t>
   </si>
@@ -656,87 +656,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -785,8 +789,11 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -805,11 +812,11 @@
       <c r="H9" s="3">
         <v>0</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J9" s="3">
-        <v>0</v>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
@@ -826,8 +833,8 @@
       <c r="O9" s="3">
         <v>0</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>4</v>
+      <c r="P9" s="3">
+        <v>0</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>4</v>
@@ -835,8 +842,11 @@
       <c r="R9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -855,11 +865,11 @@
       <c r="H10" s="3">
         <v>0</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="3">
-        <v>0</v>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
@@ -876,8 +886,8 @@
       <c r="O10" s="3">
         <v>0</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
+      <c r="P10" s="3">
+        <v>0</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>4</v>
@@ -885,8 +895,11 @@
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,8 +918,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -955,8 +969,11 @@
       <c r="R12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,8 +1022,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1055,8 +1075,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1105,8 +1128,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,13 +1148,14 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17" s="3">
         <v>0</v>
@@ -1143,11 +1170,11 @@
         <v>0</v>
       </c>
       <c r="I17" s="3">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3">
         <v>900</v>
       </c>
-      <c r="J17" s="3">
-        <v>0</v>
-      </c>
       <c r="K17" s="3">
         <v>0</v>
       </c>
@@ -1172,8 +1199,11 @@
       <c r="R17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1193,11 +1223,11 @@
         <v>0</v>
       </c>
       <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
         <v>-900</v>
       </c>
-      <c r="J18" s="3">
-        <v>0</v>
-      </c>
       <c r="K18" s="3">
         <v>0</v>
       </c>
@@ -1222,8 +1252,11 @@
       <c r="R18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,8 +1275,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1292,8 +1326,11 @@
       <c r="R20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1312,8 +1349,8 @@
       <c r="H21" s="3">
         <v>0</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
+      <c r="I21" s="3">
+        <v>0</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>4</v>
@@ -1324,8 +1361,8 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M21" s="3">
-        <v>0</v>
+      <c r="M21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N21" s="3">
         <v>0</v>
@@ -1336,14 +1373,17 @@
       <c r="P21" s="3">
         <v>0</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
+      <c r="Q21" s="3">
+        <v>0</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1392,8 +1432,11 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1413,11 +1456,11 @@
         <v>0</v>
       </c>
       <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
         <v>-900</v>
       </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
       <c r="K23" s="3">
         <v>0</v>
       </c>
@@ -1442,8 +1485,11 @@
       <c r="R23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1492,8 +1538,11 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,8 +1591,11 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1563,11 +1615,11 @@
         <v>0</v>
       </c>
       <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
         <v>-900</v>
       </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
       <c r="K26" s="3">
         <v>0</v>
       </c>
@@ -1592,8 +1644,11 @@
       <c r="R26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1613,11 +1668,11 @@
         <v>0</v>
       </c>
       <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
         <v>-900</v>
       </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
       <c r="K27" s="3">
         <v>0</v>
       </c>
@@ -1642,8 +1697,11 @@
       <c r="R27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1742,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,8 +1909,11 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1892,8 +1962,11 @@
       <c r="R32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1913,11 +1986,11 @@
         <v>0</v>
       </c>
       <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
         <v>-900</v>
       </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
       <c r="K33" s="3">
         <v>0</v>
       </c>
@@ -1942,8 +2015,11 @@
       <c r="R33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,8 +2068,11 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2013,11 +2092,11 @@
         <v>0</v>
       </c>
       <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
         <v>-900</v>
       </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
       <c r="K35" s="3">
         <v>0</v>
       </c>
@@ -2042,63 +2121,69 @@
       <c r="R35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,8 +2223,9 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2146,11 +2233,11 @@
         <v>0</v>
       </c>
       <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
         <v>100</v>
       </c>
-      <c r="F41" s="3">
-        <v>0</v>
-      </c>
       <c r="G41" s="3">
         <v>0</v>
       </c>
@@ -2161,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
         <v>100</v>
       </c>
-      <c r="K41" s="3">
-        <v>0</v>
-      </c>
       <c r="L41" s="3">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3">
         <v>100</v>
-      </c>
-      <c r="M41" s="3">
-        <v>200</v>
       </c>
       <c r="N41" s="3">
         <v>200</v>
@@ -2179,16 +2266,19 @@
         <v>200</v>
       </c>
       <c r="P41" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q41" s="3">
         <v>300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2237,8 +2327,11 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2251,8 +2344,8 @@
       <c r="F43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G43" s="3">
-        <v>0</v>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H43" s="3">
         <v>0</v>
@@ -2263,8 +2356,8 @@
       <c r="J43" s="3">
         <v>0</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>4</v>
+      <c r="K43" s="3">
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>4</v>
@@ -2281,14 +2374,17 @@
       <c r="P43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2329,16 +2425,19 @@
         <v>200</v>
       </c>
       <c r="P44" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q44" s="3">
         <v>100</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2387,8 +2486,11 @@
       <c r="R45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2417,28 +2519,31 @@
         <v>200</v>
       </c>
       <c r="L46" s="3">
+        <v>200</v>
+      </c>
+      <c r="M46" s="3">
         <v>300</v>
-      </c>
-      <c r="M46" s="3">
-        <v>400</v>
       </c>
       <c r="N46" s="3">
         <v>400</v>
       </c>
       <c r="O46" s="3">
+        <v>400</v>
+      </c>
+      <c r="P46" s="3">
         <v>500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2487,8 +2592,11 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2523,7 +2631,7 @@
         <v>0</v>
       </c>
       <c r="N48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3">
         <v>100</v>
@@ -2531,14 +2639,17 @@
       <c r="P48" s="3">
         <v>100</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>4</v>
+      <c r="Q48" s="3">
+        <v>100</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2587,8 +2698,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,8 +2804,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2698,8 +2818,8 @@
       <c r="E52" s="3">
         <v>0</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
+      <c r="F52" s="3">
+        <v>0</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>4</v>
@@ -2710,17 +2830,17 @@
       <c r="I52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>4</v>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>4</v>
@@ -2737,8 +2857,11 @@
       <c r="R52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,8 +2910,11 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -2811,7 +2937,7 @@
         <v>200</v>
       </c>
       <c r="J54" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K54" s="3">
         <v>300</v>
@@ -2820,7 +2946,7 @@
         <v>300</v>
       </c>
       <c r="M54" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N54" s="3">
         <v>500</v>
@@ -2829,16 +2955,19 @@
         <v>500</v>
       </c>
       <c r="P54" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q54" s="3">
         <v>400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,8 +3007,9 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2910,7 +3041,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N57" s="3">
         <v>100</v>
@@ -2918,8 +3049,8 @@
       <c r="O57" s="3">
         <v>100</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>4</v>
+      <c r="P57" s="3">
+        <v>100</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>4</v>
@@ -2927,8 +3058,11 @@
       <c r="R57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2977,8 +3111,11 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3027,8 +3164,11 @@
       <c r="R59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3060,16 +3200,16 @@
         <v>0</v>
       </c>
       <c r="M60" s="3">
+        <v>0</v>
+      </c>
+      <c r="N60" s="3">
         <v>200</v>
-      </c>
-      <c r="N60" s="3">
-        <v>100</v>
       </c>
       <c r="O60" s="3">
         <v>100</v>
       </c>
       <c r="P60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q60" s="3">
         <v>0</v>
@@ -3077,8 +3217,11 @@
       <c r="R60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3127,13 +3270,16 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E62" s="3">
         <v>100</v>
@@ -3142,7 +3288,7 @@
         <v>100</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H62" s="3">
         <v>0</v>
@@ -3153,11 +3299,11 @@
       <c r="J62" s="3">
         <v>0</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -3171,14 +3317,17 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>4</v>
+      <c r="Q62" s="3">
+        <v>0</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,13 +3482,16 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E66" s="3">
         <v>100</v>
@@ -3348,7 +3506,7 @@
         <v>100</v>
       </c>
       <c r="I66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J66" s="3">
         <v>0</v>
@@ -3360,7 +3518,7 @@
         <v>0</v>
       </c>
       <c r="M66" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N66" s="3">
         <v>200</v>
@@ -3369,16 +3527,19 @@
         <v>200</v>
       </c>
       <c r="P66" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q66" s="3">
         <v>100</v>
       </c>
-      <c r="Q66" s="3">
-        <v>0</v>
-      </c>
       <c r="R66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3547,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,8 +3768,11 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3606,7 +3780,7 @@
         <v>-1300</v>
       </c>
       <c r="E72" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="F72" s="3">
         <v>-1200</v>
@@ -3615,13 +3789,13 @@
         <v>-1200</v>
       </c>
       <c r="H72" s="3">
-        <v>-1100</v>
+        <v>-1200</v>
       </c>
       <c r="I72" s="3">
         <v>-1100</v>
       </c>
       <c r="J72" s="3">
-        <v>-200</v>
+        <v>-1100</v>
       </c>
       <c r="K72" s="3">
         <v>-200</v>
@@ -3630,7 +3804,7 @@
         <v>-200</v>
       </c>
       <c r="M72" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="N72" s="3">
         <v>-100</v>
@@ -3642,13 +3816,16 @@
         <v>-100</v>
       </c>
       <c r="Q72" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,13 +3980,16 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E76" s="3">
         <v>100</v>
@@ -3815,7 +4001,7 @@
         <v>100</v>
       </c>
       <c r="H76" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I76" s="3">
         <v>200</v>
@@ -3827,7 +4013,7 @@
         <v>200</v>
       </c>
       <c r="L76" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M76" s="3">
         <v>300</v>
@@ -3839,16 +4025,19 @@
         <v>300</v>
       </c>
       <c r="P76" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q76" s="3">
         <v>400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,63 +4086,69 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3973,11 +4168,11 @@
         <v>0</v>
       </c>
       <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
         <v>-900</v>
       </c>
-      <c r="J81" s="3">
-        <v>0</v>
-      </c>
       <c r="K81" s="3">
         <v>0</v>
       </c>
@@ -4002,8 +4197,11 @@
       <c r="R81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,8 +4220,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4072,8 +4271,11 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,8 +4536,11 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4343,20 +4560,20 @@
         <v>0</v>
       </c>
       <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
         <v>-900</v>
       </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
       <c r="K89" s="3">
         <v>0</v>
       </c>
       <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3">
         <v>-100</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
       <c r="N89" s="3">
         <v>0</v>
       </c>
@@ -4364,16 +4581,19 @@
         <v>0</v>
       </c>
       <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-200</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
       <c r="R89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,8 +4612,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4442,8 +4663,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,8 +4769,11 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4592,8 +4822,11 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,8 +4845,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4662,8 +4896,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,28 +5055,31 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>4</v>
+      <c r="I100" s="3">
+        <v>0</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>4</v>
@@ -4844,8 +5090,8 @@
       <c r="L100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -4854,16 +5100,19 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4912,8 +5161,11 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4942,11 +5194,11 @@
         <v>0</v>
       </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-100</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
         <v>0</v>
       </c>
@@ -4960,6 +5212,9 @@
         <v>0</v>
       </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>0</v>
       </c>
     </row>
